--- a/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A37F7E9-285E-4ABB-81F5-84DD05A930B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08B402B-901B-48E7-A253-56A0B0667EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14610" activeTab="5" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="143">
   <si>
     <t>Client</t>
   </si>
@@ -274,9 +274,6 @@
     <t>Preston Wolf</t>
   </si>
   <si>
-    <t>Rich Bowman</t>
-  </si>
-  <si>
     <t>Rittik Chakrabarti</t>
   </si>
   <si>
@@ -376,21 +373,12 @@
     <t>Akshat Jamad</t>
   </si>
   <si>
-    <t>Alan Frederick Hall</t>
-  </si>
-  <si>
     <t>Alberico Altieri</t>
   </si>
   <si>
-    <t>Alberto Alonso Basagoiti</t>
-  </si>
-  <si>
     <t>Albert Sung</t>
   </si>
   <si>
-    <t>Alejandro Arturo Serrano Leo</t>
-  </si>
-  <si>
     <t>Aleksandra Chadam</t>
   </si>
   <si>
@@ -443,9 +431,6 @@
   </si>
   <si>
     <t>Ali Amin</t>
-  </si>
-  <si>
-    <t>Alicia Furio</t>
   </si>
   <si>
     <t>Allen Plunk</t>
@@ -859,12 +844,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -953,7 +938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -961,7 +946,7 @@
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
         <v>30</v>
@@ -994,16 +979,16 @@
         <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="R2" t="s">
         <v>37</v>
@@ -1012,7 +997,7 @@
         <v>37</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="U2" t="s">
         <v>38</v>
@@ -1027,19 +1012,19 @@
         <v>41</v>
       </c>
       <c r="Y2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="Z2" t="s">
         <v>42</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AC2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="AD2" t="s">
         <v>43</v>
@@ -1053,13 +1038,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1067,20 +1052,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1091,19 +1076,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8E7CB8-6BED-4AC4-B6DC-18799B9D6A35}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1114,19 +1099,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71E31A4-9F7E-4D74-B894-2CAAC5377070}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1137,9 +1122,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1165,7 +1150,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1199,359 +1184,351 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
-      <c r="D13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>71</v>
       </c>
-      <c r="D14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>72</v>
       </c>
-      <c r="D15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2">
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I2">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3">
         <v>65</v>
@@ -1565,24 +1542,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1593,34 +1570,34 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76.21875" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="B2" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08B402B-901B-48E7-A253-56A0B0667EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C550D10D-E428-4ED3-9ABC-1EBA6BA3FB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14610" activeTab="5" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>

--- a/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C550D10D-E428-4ED3-9ABC-1EBA6BA3FB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB501F1-4752-4479-952F-7218010ECAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -136,9 +136,6 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -473,6 +470,9 @@
   </si>
   <si>
     <t>William Peluchiwski</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -547,9 +547,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -587,7 +587,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -693,7 +693,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -835,7 +835,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -946,88 +946,88 @@
         <v>29</v>
       </c>
       <c r="C2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
         <v>131</v>
       </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="R2" t="s">
         <v>36</v>
       </c>
-      <c r="N2" t="s">
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W2" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="R2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" t="s">
-        <v>39</v>
-      </c>
-      <c r="W2" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AB2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD2" t="s">
         <v>42</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1046,26 +1046,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1083,12 +1083,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1106,12 +1106,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1126,54 +1126,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>55</v>
-      </c>
-      <c r="D2" t="s">
-        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1193,300 +1193,300 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1506,21 +1506,21 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2">
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I2">
         <v>25</v>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3">
         <v>65</v>
@@ -1549,17 +1549,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1578,26 +1578,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB501F1-4752-4479-952F-7218010ECAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A3CC66-CE95-42A5-B4AF-1628066F5999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -469,10 +469,10 @@
     <t>9999</t>
   </si>
   <si>
-    <t>William Peluchiwski</t>
-  </si>
-  <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>James Craven</t>
   </si>
 </sst>
 </file>
@@ -949,7 +949,7 @@
         <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -979,7 +979,7 @@
         <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>132</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
         <v>135</v>

--- a/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A3CC66-CE95-42A5-B4AF-1628066F5999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C44EB7C-57CB-429C-B868-80625D4FEF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="142">
   <si>
     <t>Client</t>
   </si>
@@ -404,9 +404,6 @@
   </si>
   <si>
     <t>Alex Lerer</t>
-  </si>
-  <si>
-    <t>Alex Maffei</t>
   </si>
   <si>
     <t>Alex Orlean</t>
@@ -479,7 +476,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,6 +488,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -516,7 +520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -529,6 +533,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,12 +849,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -938,7 +943,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -946,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -979,16 +984,16 @@
         <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R2" t="s">
         <v>36</v>
@@ -997,7 +1002,7 @@
         <v>36</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="U2" t="s">
         <v>37</v>
@@ -1012,19 +1017,19 @@
         <v>40</v>
       </c>
       <c r="Y2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Z2" t="s">
         <v>41</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AC2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD2" t="s">
         <v>42</v>
@@ -1038,13 +1043,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1052,20 +1057,20 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1076,19 +1081,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8E7CB8-6BED-4AC4-B6DC-18799B9D6A35}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1104,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71E31A4-9F7E-4D74-B894-2CAAC5377070}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1122,9 +1127,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1150,7 +1155,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1184,307 +1189,301 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>58</v>
       </c>
-      <c r="D2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>59</v>
       </c>
-      <c r="D3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>60</v>
       </c>
-      <c r="D4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>61</v>
       </c>
-      <c r="D5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>62</v>
       </c>
-      <c r="D6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>63</v>
       </c>
-      <c r="D7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>121</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>115</v>
       </c>
@@ -1498,13 +1497,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1512,7 +1511,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -1526,7 +1525,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>90</v>
       </c>
@@ -1542,24 +1541,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1570,13 +1569,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="76.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="76.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>85</v>
       </c>
@@ -1584,20 +1583,20 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C44EB7C-57CB-429C-B868-80625D4FEF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DE799B-5284-46D3-A9F4-CE40671E82A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>

--- a/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DE799B-5284-46D3-A9F4-CE40671E82A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBF6A79-2AFE-4E92-897E-62D9D4BE9843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -466,10 +463,13 @@
     <t>9999</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>James Craven</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -851,7 +851,8 @@
   <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
@@ -865,174 +866,174 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>139</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="U2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC2" t="s">
         <v>129</v>
       </c>
-      <c r="D2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" t="s">
-        <v>141</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="R2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="U2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" t="s">
-        <v>38</v>
-      </c>
-      <c r="W2" t="s">
-        <v>39</v>
-      </c>
-      <c r="X2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AD2" t="s">
         <v>41</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1051,26 +1052,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1088,12 +1089,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1111,12 +1112,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1131,54 +1132,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>54</v>
-      </c>
-      <c r="D2" t="s">
-        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1198,294 +1199,294 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1505,21 +1506,21 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2">
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I2">
         <v>25</v>
@@ -1527,7 +1528,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3">
         <v>65</v>
@@ -1548,17 +1549,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1577,26 +1578,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBF6A79-2AFE-4E92-897E-62D9D4BE9843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E87404-5FC9-4C9D-892A-AF762F67D0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -849,13 +849,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -944,7 +944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1044,13 +1044,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>129</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>139</v>
       </c>
@@ -1082,17 +1082,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8E7CB8-6BED-4AC4-B6DC-18799B9D6A35}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -1105,17 +1105,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71E31A4-9F7E-4D74-B894-2CAAC5377070}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>137</v>
       </c>
@@ -1128,9 +1128,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1190,49 +1190,49 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>65</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>117</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -1272,62 +1272,62 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -1335,67 +1335,67 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>119</v>
       </c>
@@ -1403,32 +1403,32 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>120</v>
       </c>
@@ -1436,47 +1436,47 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>123</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>114</v>
       </c>
@@ -1498,13 +1498,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -1542,22 +1542,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -1570,13 +1570,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>84</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>86</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>86</v>
       </c>

--- a/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F81BA3-6AD2-4CF1-9C6F-C506B29F3861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0806140-9FAE-410A-9C39-19047CC1FA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,7 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Brian Miller</t>
+    <t>Jennie Stewart</t>
   </si>
 </sst>
 </file>
@@ -849,14 +849,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -945,7 +945,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1045,13 +1045,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>129</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -1083,17 +1083,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8E7CB8-6BED-4AC4-B6DC-18799B9D6A35}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>134</v>
       </c>
@@ -1106,17 +1106,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71E31A4-9F7E-4D74-B894-2CAAC5377070}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -1129,9 +1129,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1191,49 +1191,49 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>116</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>65</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>117</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -1273,62 +1273,62 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -1336,67 +1336,67 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>119</v>
       </c>
@@ -1404,32 +1404,32 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>120</v>
       </c>
@@ -1437,47 +1437,47 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>123</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>114</v>
       </c>
@@ -1499,13 +1499,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -1543,22 +1543,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -1571,13 +1571,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="76.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="76.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>84</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>86</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>86</v>
       </c>

--- a/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035665_VerifyInternalDealTeamForAnalystRoleLimitForCFLOBOpportunityEngagement.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0806140-9FAE-410A-9C39-19047CC1FA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D67FA0-9293-4B36-9D6D-23BEF4DBB519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
-    <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="AppName" sheetId="8" r:id="rId3"/>
-    <sheet name="ModuleName" sheetId="9" r:id="rId4"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
+    <sheet name="AppName" sheetId="8" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="9" r:id="rId3"/>
+    <sheet name="AddOpportunity" sheetId="1" r:id="rId4"/>
     <sheet name="AddContact" sheetId="3" r:id="rId5"/>
     <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId6"/>
     <sheet name="Roles" sheetId="7" r:id="rId7"/>
@@ -847,194 +847,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
-  <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>138</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="R2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="U2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W2" t="s">
-        <v>38</v>
-      </c>
-      <c r="X2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>41</v>
+      <c r="B3" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1043,36 +885,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8E7CB8-6BED-4AC4-B6DC-18799B9D6A35}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1081,21 +908,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8E7CB8-6BED-4AC4-B6DC-18799B9D6A35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71E31A4-9F7E-4D74-B894-2CAAC5377070}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1104,21 +931,194 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71E31A4-9F7E-4D74-B894-2CAAC5377070}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
+  <dimension ref="A1:AD2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>138</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="U2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1129,9 +1129,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1191,49 +1191,49 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>65</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>117</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -1273,62 +1273,62 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -1336,67 +1336,67 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>119</v>
       </c>
@@ -1404,32 +1404,32 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>120</v>
       </c>
@@ -1437,47 +1437,47 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>123</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>114</v>
       </c>
@@ -1499,13 +1499,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -1543,22 +1543,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -1571,13 +1571,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>84</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>86</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>86</v>
       </c>
